--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536134_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536134_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,28 +724,28 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5466</v>
+        <v>3.1616</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3076</v>
+        <v>1.9227</v>
       </c>
       <c r="F4" t="n">
         <v>1.239</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1601</v>
+        <v>0.7752</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0804</v>
+        <v>-0.4653</v>
       </c>
       <c r="I4" t="n">
         <v>1.2405</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1806</v>
+        <v>1.7957</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.455</v>
+        <v>0.16</v>
       </c>
       <c r="L4" t="n">
         <v>1.6356</v>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>J. CHARLES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.915</v>
+        <v>0.7667</v>
       </c>
       <c r="E6" t="n">
-        <v>0.915</v>
+        <v>1.3211</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.5543</v>
       </c>
       <c r="G6" t="n">
-        <v>0.915</v>
+        <v>1.0918</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3075</v>
+        <v>0.7904</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6075</v>
+        <v>0.3014</v>
       </c>
       <c r="J6" t="n">
-        <v>0.915</v>
+        <v>1.7777</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3075</v>
+        <v>1.6157</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6075</v>
+        <v>0.162</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.6858</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8252</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.1394</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9749</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.195</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1699</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.1986</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.2616</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.4602</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.4986</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CHARLES</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7667</v>
+        <v>0.6016</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3211</v>
+        <v>0.3027</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5543</v>
+        <v>0.2989</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0918</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7904</v>
+        <v>1.7387</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3014</v>
+        <v>-1.8324</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7777</v>
+        <v>1.6138</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6157</v>
+        <v>3.4529</v>
       </c>
       <c r="L7" t="n">
-        <v>0.162</v>
+        <v>-1.839</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6858</v>
+        <v>-1.7076</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8252</v>
+        <v>-1.7142</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1394</v>
+        <v>0.0066</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9749</v>
+        <v>0.585</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.195</v>
+        <v>-1.1699</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1699</v>
+        <v>1.7549</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1986</v>
+        <v>0.389</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2616</v>
+        <v>-0.1412</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4602</v>
+        <v>0.5302</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4986</v>
+        <v>-0.2786</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4986</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.615</v>
+        <v>0.4617</v>
       </c>
       <c r="E8" t="n">
-        <v>0.615</v>
+        <v>-0.306</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.7677</v>
       </c>
       <c r="G8" t="n">
-        <v>0.615</v>
+        <v>-1.0925</v>
       </c>
       <c r="H8" t="n">
-        <v>0.615</v>
+        <v>-0.8349</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.2576</v>
       </c>
       <c r="J8" t="n">
-        <v>0.615</v>
+        <v>-0.5495</v>
       </c>
       <c r="K8" t="n">
-        <v>0.615</v>
+        <v>-0.5575</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.543</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.2774</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.2656</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.585</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.585</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.3062</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.2435</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6629</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6629</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,58 +1139,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6016</v>
+        <v>-0.7783</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3027</v>
+        <v>-0.1871</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2989</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.4713</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7387</v>
+        <v>1.152</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8324</v>
+        <v>-1.6234</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6138</v>
+        <v>-0.004</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4529</v>
+        <v>0.6765</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.839</v>
+        <v>-0.6805</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7076</v>
+        <v>-0.4673</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7142</v>
+        <v>0.4755</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0066</v>
+        <v>-0.9428</v>
       </c>
       <c r="P9" t="n">
-        <v>0.585</v>
+        <v>0.195</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1699</v>
+        <v>-0.195</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7549</v>
+        <v>0.39</v>
       </c>
       <c r="S9" t="n">
-        <v>0.389</v>
+        <v>-0.2235</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1412</v>
+        <v>0.0118</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5302</v>
+        <v>-0.2353</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2786</v>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>D. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4617</v>
+        <v>-1.8269</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.306</v>
+        <v>-0.1382</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7677</v>
+        <v>-1.6888</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0925</v>
+        <v>1.254</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8349</v>
+        <v>0.0017</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2576</v>
+        <v>1.2523</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5495</v>
+        <v>1.9282</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5575</v>
+        <v>0.0086</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008</v>
+        <v>1.9196</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.543</v>
+        <v>-0.6742</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2774</v>
+        <v>-0.0069</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2656</v>
+        <v>-0.6673</v>
       </c>
       <c r="P10" t="n">
-        <v>0.585</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9248</v>
       </c>
       <c r="R10" t="n">
-        <v>0.585</v>
+        <v>1.5599</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3062</v>
+        <v>0.3926</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2435</v>
+        <v>0.5799</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06270000000000001</v>
+        <v>-0.1873</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6629</v>
+        <v>-2.1086</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6629</v>
+        <v>-2.3872</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,58 +1305,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7783</v>
+        <v>-2.4133</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1871</v>
+        <v>-2.5365</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0.1232</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4713</v>
+        <v>-1.1984</v>
       </c>
       <c r="H11" t="n">
-        <v>1.152</v>
+        <v>-0.2085</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6234</v>
+        <v>-0.9899</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.004</v>
+        <v>-0.452</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6765</v>
+        <v>0.1395</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6805</v>
+        <v>-0.5915</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4673</v>
+        <v>-0.7464</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4755</v>
+        <v>-0.348</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9428</v>
+        <v>-0.3984</v>
       </c>
       <c r="P11" t="n">
-        <v>0.195</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.195</v>
+        <v>-1.9499</v>
       </c>
       <c r="R11" t="n">
-        <v>0.39</v>
+        <v>1.1699</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2235</v>
+        <v>-0.1564</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0118</v>
+        <v>-0.1347</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2353</v>
+        <v>-0.0217</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2786</v>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>D. WALTON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4133</v>
+        <v>-3.996</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5365</v>
+        <v>-4.7112</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1232</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1984</v>
+        <v>-4.1391</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2085</v>
+        <v>-3.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9899</v>
+        <v>-1.0855</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.452</v>
+        <v>-3.8716</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1395</v>
+        <v>-3.3206</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5915</v>
+        <v>-0.551</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7464</v>
+        <v>-0.2675</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.348</v>
+        <v>0.267</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3984</v>
+        <v>-0.5345</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7799</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1699</v>
+        <v>0.9749</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1564</v>
+        <v>-0.1021</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1347</v>
+        <v>-0.1098</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0217</v>
+        <v>0.0077</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2786</v>
+        <v>1.2201</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. GONZALEZ LONGARELA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,150 +1471,146 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.742</v>
+        <v>4.136099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0532</v>
+        <v>1.139600000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6888</v>
+        <v>2.996599999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3389</v>
+        <v>-0.4356000000000004</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3058</v>
+        <v>-4.4363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6447000000000001</v>
+        <v>4.0008</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0131</v>
+        <v>7.0538</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2989</v>
+        <v>1.0938</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3121</v>
+        <v>5.959999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6742</v>
+        <v>-7.4892</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0069</v>
+        <v>-5.530299999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6673</v>
+        <v>-1.959</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3649</v>
+        <v>1.9501</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9248</v>
+        <v>-11.6993</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5599</v>
+        <v>13.6491</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3926</v>
+        <v>1.7471</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5799</v>
+        <v>0.4004</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1873</v>
+        <v>1.3465</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1086</v>
+        <v>0.8746000000000005</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2786</v>
+        <v>5.384600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3872</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536134_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-4.51</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. WALTON</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>SPANISH BASKETBALL ACADEMY</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.996</v>
+        <v>5.5878</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.7112</v>
+        <v>4.0495</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7151999999999999</v>
+        <v>1.5382</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.1391</v>
+        <v>2.7908</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.0535</v>
+        <v>2.2073</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0855</v>
+        <v>0.5835</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.8716</v>
+        <v>2.4352</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.3206</v>
+        <v>1.7387</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.551</v>
+        <v>0.6965</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2675</v>
+        <v>0.3556</v>
       </c>
       <c r="N14" t="n">
-        <v>0.267</v>
+        <v>0.4686</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5345</v>
+        <v>-0.113</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9749</v>
+        <v>1.7549</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9749</v>
+        <v>1.7549</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1021</v>
+        <v>-0.5094</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1098</v>
+        <v>-0.2158</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0077</v>
+        <v>-0.2937</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2201</v>
+        <v>1.5515</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2201</v>
+        <v>1.8301</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1625,86 +1621,90 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>SPANISH BASKETBALL ACADEMY</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.136000000000001</v>
+        <v>2.5955</v>
       </c>
       <c r="E15" t="n">
-        <v>1.139500000000002</v>
+        <v>0.1774</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9966</v>
+        <v>2.4181</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4358000000000004</v>
+        <v>2.2665</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.4364</v>
+        <v>2.4869</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0007</v>
+        <v>-0.2204</v>
       </c>
       <c r="J15" t="n">
-        <v>7.0536</v>
+        <v>0.9646</v>
       </c>
       <c r="K15" t="n">
-        <v>1.093799999999999</v>
+        <v>1.7426</v>
       </c>
       <c r="L15" t="n">
-        <v>5.959999999999999</v>
+        <v>-0.778</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.489199999999999</v>
+        <v>1.3019</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.530299999999999</v>
+        <v>0.7443</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.959</v>
+        <v>0.5576</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9501</v>
+        <v>-0.195</v>
       </c>
       <c r="Q15" t="n">
-        <v>-11.6993</v>
+        <v>-1.9499</v>
       </c>
       <c r="R15" t="n">
-        <v>13.6491</v>
+        <v>1.7549</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7471</v>
+        <v>-0.4175</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4004</v>
+        <v>-0.0574</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3465</v>
+        <v>-0.36</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8746000000000005</v>
+        <v>0.9415</v>
       </c>
       <c r="W15" t="n">
-        <v>5.384600000000001</v>
+        <v>1.2201</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.51</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+        <v>-0.2786</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2536134_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>T. TRIFONOV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5878</v>
+        <v>1.4012</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0495</v>
+        <v>0.4511</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5382</v>
+        <v>0.9502</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7908</v>
+        <v>1.1372</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2073</v>
+        <v>0.5928</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5835</v>
+        <v>0.5444</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4352</v>
+        <v>0.3895</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7387</v>
+        <v>0.3895</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6965</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3556</v>
+        <v>0.7477</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4686</v>
+        <v>0.2033</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.113</v>
+        <v>0.5444</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7549</v>
+        <v>0.39</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7549</v>
+        <v>0.39</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5094</v>
+        <v>-0.126</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2158</v>
+        <v>0.0615</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2937</v>
+        <v>-0.1875</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5515</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8301</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>D. LOPEZ RIANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5955</v>
+        <v>0.404</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1774</v>
+        <v>-0.1462</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4181</v>
+        <v>0.5502</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2665</v>
+        <v>0.2809</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4869</v>
+        <v>0.5951</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2204</v>
+        <v>-0.3141</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9646</v>
+        <v>0.5486</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7426</v>
+        <v>0.4676</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.778</v>
+        <v>0.081</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3019</v>
+        <v>-0.2676</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7443</v>
+        <v>0.1275</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5576</v>
+        <v>-0.3951</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.195</v>
+        <v>0.9749</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7549</v>
+        <v>0.9749</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4175</v>
+        <v>-0.2418</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0574</v>
+        <v>-0.6948</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.36</v>
+        <v>0.453</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9415</v>
+        <v>-0.61</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2786</v>
+        <v>-0.61</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. TRIFONOV</t>
+          <t>W. TSAFACK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,40 +1882,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4012</v>
+        <v>0.1414</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4511</v>
+        <v>-0.2971</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9502</v>
+        <v>0.4385</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1372</v>
+        <v>-0.4426</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5928</v>
+        <v>-0.4459</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5444</v>
+        <v>0.0033</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3895</v>
+        <v>-0.377</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3895</v>
+        <v>-0.377</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7477</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2033</v>
+        <v>-0.0689</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5444</v>
+        <v>0.0033</v>
       </c>
       <c r="P18" t="n">
         <v>0.39</v>
@@ -1927,13 +1927,13 @@
         <v>0.39</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.126</v>
+        <v>0.194</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0615</v>
+        <v>0.0799</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1875</v>
+        <v>0.1141</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. LOPEZ RIANO</t>
+          <t>B. GONZALEZ RAMIREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.404</v>
+        <v>0.1174</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1462</v>
+        <v>-1.9422</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5502</v>
+        <v>2.0596</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2809</v>
+        <v>1.0701</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5951</v>
+        <v>-0.4755</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3141</v>
+        <v>1.5456</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5486</v>
+        <v>0.2471</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4676</v>
+        <v>-1.0165</v>
       </c>
       <c r="L19" t="n">
-        <v>0.081</v>
+        <v>1.2636</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2676</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1275</v>
+        <v>0.541</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3951</v>
+        <v>0.2821</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9749</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9749</v>
+        <v>1.1699</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2418</v>
+        <v>-0.1728</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6948</v>
+        <v>-0.2394</v>
       </c>
       <c r="U19" t="n">
-        <v>0.453</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.61</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.61</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. TSAFACK</t>
+          <t>H. SANTA CRUZ CARDENAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,64 +2048,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1414</v>
+        <v>-0.9228</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2971</v>
+        <v>-2.0599</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4385</v>
+        <v>1.1371</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4426</v>
+        <v>0.4109</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4459</v>
+        <v>-0.6002</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0033</v>
+        <v>1.0111</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.377</v>
+        <v>0.065</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.377</v>
+        <v>-0.664</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.729</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.3458</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0689</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0033</v>
+        <v>0.2821</v>
       </c>
       <c r="P20" t="n">
-        <v>0.39</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R20" t="n">
-        <v>0.39</v>
+        <v>1.1699</v>
       </c>
       <c r="S20" t="n">
-        <v>0.194</v>
+        <v>-0.4479</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0799</v>
+        <v>-0.0693</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1141</v>
+        <v>-0.3786</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1058</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.1058</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. GONZALEZ RAMIREZ</t>
+          <t>K. EZEAGU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1174</v>
+        <v>-1.0771</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9422</v>
+        <v>-0.6834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0596</v>
+        <v>-0.3937</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0701</v>
+        <v>0.1996</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4755</v>
+        <v>1.1942</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5456</v>
+        <v>-0.9946</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2471</v>
+        <v>2.0923</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0165</v>
+        <v>1.4768</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2636</v>
+        <v>0.6155</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8231000000000001</v>
+        <v>-1.8927</v>
       </c>
       <c r="N21" t="n">
-        <v>0.541</v>
+        <v>-0.2825</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2821</v>
+        <v>-1.6102</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7799</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1699</v>
+        <v>0.9749</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1728</v>
+        <v>0.4141</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2394</v>
+        <v>-0.3885</v>
       </c>
       <c r="U21" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.8026</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.7159</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.4373</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. SANTA CRUZ CARDENAL</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9228</v>
+        <v>-2.7564</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0599</v>
+        <v>-1.2171</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1371</v>
+        <v>-1.5393</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4109</v>
+        <v>-2.0016</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6002</v>
+        <v>-0.9584</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0111</v>
+        <v>-1.0432</v>
       </c>
       <c r="J22" t="n">
-        <v>0.065</v>
+        <v>0.6357</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.664</v>
+        <v>-0.0608</v>
       </c>
       <c r="L22" t="n">
-        <v>0.729</v>
+        <v>0.6965</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3458</v>
+        <v>-2.6373</v>
       </c>
       <c r="N22" t="n">
-        <v>0.06370000000000001</v>
+        <v>-0.8976</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2821</v>
+        <v>-1.7397</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7799</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9499</v>
+        <v>-2.9248</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1699</v>
+        <v>1.3649</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4479</v>
+        <v>0.195</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0693</v>
+        <v>0.1834</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3786</v>
+        <v>0.0116</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1058</v>
+        <v>0.61</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.1058</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. EZEAGU</t>
+          <t>N. BILAMU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,40 +2297,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0771</v>
+        <v>-3.8707</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6834</v>
+        <v>-1.0453</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3937</v>
+        <v>-2.8253</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1996</v>
+        <v>-1.7868</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1942</v>
+        <v>0.1606</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9946</v>
+        <v>-1.9474</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0923</v>
+        <v>1.0586</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4768</v>
+        <v>1.1236</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6155</v>
+        <v>-0.065</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8927</v>
+        <v>-2.8454</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2825</v>
+        <v>-0.963</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6102</v>
+        <v>-1.8824</v>
       </c>
       <c r="P23" t="n">
         <v>-0.9749</v>
@@ -2342,22 +2342,22 @@
         <v>0.9749</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4141</v>
+        <v>0.2169</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3885</v>
+        <v>-0.0483</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8026</v>
+        <v>0.2652</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7159</v>
+        <v>-1.3259</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.4373</v>
+        <v>-0.1058</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>N. PETRONE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7564</v>
+        <v>-4.7816</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2171</v>
+        <v>-0.2833</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5393</v>
+        <v>-4.4983</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.0016</v>
+        <v>-3.4896</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9584</v>
+        <v>-0.3206</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0432</v>
+        <v>-3.169</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6357</v>
+        <v>-0.5704</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0608</v>
+        <v>0.7096</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6965</v>
+        <v>-1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6373</v>
+        <v>-2.9192</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8976</v>
+        <v>-1.0302</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7397</v>
+        <v>-1.889</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5599</v>
+        <v>-0.195</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9248</v>
+        <v>-0.9749</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3649</v>
+        <v>0.7799</v>
       </c>
       <c r="S24" t="n">
-        <v>0.195</v>
+        <v>0.1231</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1834</v>
+        <v>0.042</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0116</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.61</v>
+        <v>-1.2201</v>
       </c>
       <c r="W24" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.2201</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2786</v>
+        <v>-2.4401</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N. BILAMU</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,235 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8707</v>
+        <v>-3.161300000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0453</v>
+        <v>-2.996499999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8253</v>
+        <v>-0.1646999999999998</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.7868</v>
+        <v>0.4354000000000005</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1606</v>
+        <v>4.4363</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9474</v>
+        <v>-4.0008</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0586</v>
+        <v>7.489199999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1236</v>
+        <v>5.5301</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.065</v>
+        <v>1.9591</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.8454</v>
+        <v>-7.0537</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.963</v>
+        <v>-1.0938</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.8824</v>
+        <v>-5.9599</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9749</v>
+        <v>-1.9497</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.9499</v>
+        <v>-13.6492</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9749</v>
+        <v>11.6991</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2169</v>
+        <v>-0.7722999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0483</v>
+        <v>-1.3467</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2652</v>
+        <v>0.5744</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.3259</v>
+        <v>-0.8746999999999996</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1058</v>
+        <v>4.51</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536134_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>N. PETRONE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-4.7816</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.2833</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-4.4983</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-3.4896</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-0.3206</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-3.169</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-0.5704</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.7096</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-2.9192</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-1.0302</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-1.889</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-0.195</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-0.9749</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.7799</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.1231</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.08110000000000001</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.2201</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-2.4401</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536134_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-3.161300000000001</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-2.996499999999999</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0.1646999999999998</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.4354000000000005</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4.4363</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-4.0008</v>
-      </c>
-      <c r="J27" t="n">
-        <v>7.489199999999999</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5.5301</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.9591</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-7.0537</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-1.0938</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-5.9599</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-1.9497</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-13.6492</v>
-      </c>
-      <c r="R27" t="n">
-        <v>11.6991</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-0.7722999999999999</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-1.3467</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.5744</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-0.8746999999999996</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="X27" t="n">
         <v>-5.3846</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
